--- a/experiments/results/resnet34/CIFAR-10/ReAct/adaptive/max/results.xlsx
+++ b/experiments/results/resnet34/CIFAR-10/ReAct/adaptive/max/results.xlsx
@@ -353,7 +353,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:O10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="61.33203125" customWidth="1" style="3" min="15" max="15"/>
@@ -666,6 +666,202 @@
       <c r="O6" s="5" t="inlineStr">
         <is>
           <t>dice_p=None,ash_p=None,react_th=1.2,scale_th=3.5,type=max</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
+        <v>15.04</v>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>97.36</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>28.94</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>94.06</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>98.70999999999999</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>96.72</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>99.76000000000001</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>5.81</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>98.73</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>12.68</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>97.56</v>
+      </c>
+      <c r="O7" s="5" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=1.1,scale_th=3.0,type=max</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="n">
+        <v>14.89</v>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>97.36</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>28.33</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>94.18000000000001</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>98.75</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>18.55</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>96.84</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>99.77</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>98.78</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>12.29</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>97.61</v>
+      </c>
+      <c r="O8" s="5" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=1.1,scale_th=10.0,type=max</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n">
+        <v>15.11</v>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>97.36</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>29.16</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>94.09</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>19.31</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>96.73</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>98.72</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>12.79</v>
+      </c>
+      <c r="N9" s="5" t="n">
+        <v>97.56</v>
+      </c>
+      <c r="O9" s="5" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=1.0,scale_th=3.0,type=max</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>97.36</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>28.46</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>94.20999999999999</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>98.73999999999999</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>18.53</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>96.86</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>99.76000000000001</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>5.54</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>98.76000000000001</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>12.38</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>97.62</v>
+      </c>
+      <c r="O10" s="5" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=1.0,scale_th=10.0,type=max</t>
         </is>
       </c>
     </row>
